--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,40 +446,50 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ETD</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Vessel</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Voyage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ETD</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>POD</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ETA</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>TransitDays</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Raw</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ScrapedAt</t>
         </is>
@@ -501,24 +511,453 @@
           <t>SEGOT</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>(Parse pending)</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ONE Solutions Support English HOME SCHEDULE PRICES BOOKING DOCUMENTATION MANAGE SHIPMENT FINANCE Search Schedule Search for schedules, book, and manage your shipment. User Guide Point to Point Vessel Port Long Range List Calendar POL/ POD Selection Go Green Origin Destination Date Next 2 Weeks Cargo</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:02 UTC</t>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>(Input error: Locator.click: Timeout 30000ms exceeded.
+Call log:
+waiting for locator("input").first.first
+  -   locator resolved to &lt;input id=":ri:" role="switch" type="checkbox" data-enabled="false" aria-labelledby=":ri:--label" class="mag-toggle__input mag-toggle__input--size-responsive mag-toggle__input--labelAlignment-left"/&gt;
+  - attempting click action
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #1
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #2
+  -   waiting 20ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #3
+  -   waiting 100ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #4
+  -   waiting 100ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #5
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #6
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #7
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #8
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #9
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #10
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #11
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #12
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #13
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #14
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #15
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #16
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #17
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #18
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #19
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #20
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #21
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #22
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #23
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #24
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #25
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #26
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #27
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #28
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #29
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #30
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #31
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #32
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #33
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #34
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #35
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #36
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #37
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #38
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #39
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #40
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #41
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #42
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #43
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #44
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #45
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #46
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #47
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #48
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #49
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #50
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #51
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #52
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #53
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #54
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #55
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #56
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #57
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #58
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #59
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #60
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #61
+  -   waiting 500ms
+)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-08-05 07:16 UTC</t>
         </is>
       </c>
     </row>
@@ -538,24 +977,460 @@
           <t>NOOSL</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>(Parse pending)</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ONE Solutions Support English HOME SCHEDULE PRICES BOOKING DOCUMENTATION MANAGE SHIPMENT FINANCE Search Schedule Search for schedules, book, and manage your shipment. User Guide Point to Point Vessel Port Long Range List Calendar POL/ POD Selection Go Green Origin HONG KONG, HONG KONG, CHINA (CY) De</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:02 UTC</t>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>(Input error: Locator.click: Timeout 30000ms exceeded.
+Call log:
+waiting for locator("input").first.first
+  -   locator resolved to &lt;input id=":ri:" role="switch" type="checkbox" data-enabled="false" aria-labelledby=":ri:--label" class="mag-toggle__input mag-toggle__input--size-responsive mag-toggle__input--labelAlignment-left"/&gt;
+  - attempting click action
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #1
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #2
+  -   waiting 20ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #3
+  -   waiting 100ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #4
+  -   waiting 100ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #5
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #6
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #7
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #8
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #9
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #10
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #11
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #12
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #13
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #14
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #15
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #16
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #17
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #18
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #19
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #20
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #21
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #22
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #23
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #24
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #25
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #26
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #27
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #28
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #29
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #30
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #31
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #32
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #33
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #34
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #35
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #36
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #37
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #38
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #39
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #40
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #41
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #42
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #43
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #44
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #45
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #46
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #47
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #48
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #49
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #50
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #51
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #52
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #53
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #54
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #55
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #56
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #57
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #58
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #59
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #60
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #61
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #62
+  -   waiting 500ms
+)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-08-05 07:17 UTC</t>
         </is>
       </c>
     </row>
@@ -575,24 +1450,933 @@
           <t>NOTAE</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>(Parse pending)</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ONE Solutions Support English HOME SCHEDULE PRICES BOOKING DOCUMENTATION MANAGE SHIPMENT FINANCE Search Schedule Search for schedules, book, and manage your shipment. User Guide Point to Point Vessel Port Long Range List Calendar POL/ POD Selection Go Green Origin HO CHI MINH, VIETNAM (CY) TANANGER,</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:02 UTC</t>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>(Input error: Locator.click: Timeout 30000ms exceeded.
+Call log:
+waiting for locator("input").first.first
+  -   locator resolved to &lt;input id=":ri:" role="switch" type="checkbox" data-enabled="false" aria-labelledby=":ri:--label" class="mag-toggle__input mag-toggle__input--size-responsive mag-toggle__input--labelAlignment-left"/&gt;
+  - attempting click action
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #1
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #2
+  -   waiting 20ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #3
+  -   waiting 100ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #4
+  -   waiting 100ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #5
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #6
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #7
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #8
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #9
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #10
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #11
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #12
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #13
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #14
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #15
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #16
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #17
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #18
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #19
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #20
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #21
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #22
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #23
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #24
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #25
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #26
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #27
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #28
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #29
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #30
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #31
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #32
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #33
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #34
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #35
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #36
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #37
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #38
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #39
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #40
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #41
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #42
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #43
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #44
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #45
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #46
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #47
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #48
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #49
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #50
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #51
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #52
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #53
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #54
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #55
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #56
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #57
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #58
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #59
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #60
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #61
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #62
+  -   waiting 500ms
+)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-08-05 07:18 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>(Input error: Locator.click: Timeout 30000ms exceeded.
+Call log:
+waiting for locator("input").first.first
+  -   locator resolved to &lt;input id=":ri:" role="switch" type="checkbox" data-enabled="false" aria-labelledby=":ri:--label" class="mag-toggle__input mag-toggle__input--size-responsive mag-toggle__input--labelAlignment-left"/&gt;
+  - attempting click action
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #1
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #2
+  -   waiting 20ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #3
+  -   waiting 100ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #4
+  -   waiting 100ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #5
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #6
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #7
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #8
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #9
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #10
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #11
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #12
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #13
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #14
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #15
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #16
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #17
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #18
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #19
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #20
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #21
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #22
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #23
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #24
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #25
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #26
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #27
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #28
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #29
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #30
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #31
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #32
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #33
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #34
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #35
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #36
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #37
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #38
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #39
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #40
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #41
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #42
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #43
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #44
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #45
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #46
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #47
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #48
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #49
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #50
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #51
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #52
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #53
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #54
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #55
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #56
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #57
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #58
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #59
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #60
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #61
+  -   waiting 500ms
+  -   waiting for element to be visible, enabled and stable
+  -   element is visible, enabled and stable
+  -   scrolling into view if needed
+  -   done scrolling
+  -   &lt;label for=":ri:" id=":ri:--root" class="mag-toggle__base mag-toggle__base--size-responsive mag-toggle__base--labelAlignment-left"&gt;…&lt;/label&gt; intercepts pointer events
+  - retrying click action, attempt #62
+  -   waiting 500ms
+)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-08-05 07:18 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:48 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -1114,96 +1114,60 @@
           <t>NOOSL</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>HONG KONG</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SX1</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ONE MAGDALENA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ONE MAGDALENA 2630W</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ROTTERDAM</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (2)</t>
-        </is>
-      </c>
+          <t>(Error: None)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SX1</t>
-        </is>
-      </c>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CAPE ARTEMISIO FI631A</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1177,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,49 +1192,45 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>JSM</t>
-        </is>
-      </c>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>EMMANUEL P 012S</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1240,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,49 +1255,45 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>JSM</t>
-        </is>
-      </c>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>EMMANUEL P 012S</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1347,64 +1303,60 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>JSM</t>
-        </is>
-      </c>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 016S</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1366,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,49 +1381,45 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>JSM</t>
-        </is>
-      </c>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 016S</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,64 +1429,60 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SX1</t>
-        </is>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SEASPAN BELIEF</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SEASPAN BELIEF 2632W</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1553,7 +1497,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,49 +1507,45 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SX1</t>
-        </is>
-      </c>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MSC SHREYA B</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MSC SHREYA B FI633A</t>
+          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1620,265 +1560,265 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>YM COSMOS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 186S</t>
+          <t>YM COSMOS 191E</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ONE ORINOCO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 186S</t>
+          <t>ONE ORINOCO 2630E</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ESPIRITO SANTO EXPRESS</t>
+          <t>HMM OSLO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ESPIRITO SANTO EXPRESS 2634W</t>
+          <t>HMM OSLO 020W</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>64</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>HMM OSLO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1188S</t>
+          <t>HMM OSLO 020W</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1888,525 +1828,553 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>YM MOBILITY</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1188S</t>
+          <t>YM MOBILITY 090E</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>AX3</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>TENO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>TENO 2631E</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>FE3</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>ONE FUTURE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>ONE FUTURE 009W</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>64</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>FE3</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>ONE FUTURE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>ONE FUTURE 009W</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PN3</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>HYUNDAI FORWARD</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>HYUNDAI FORWARD 171E</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>AX3</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>SEASPAN ZAMBEZI</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>SEASPAN ZAMBEZI 2632E</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PN3</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>ONE MODERN</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>ONE MODERN 082E</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>FE3</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>HMM LE HAVRE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>TAN CANG CAI MEP INTERNATIONAL TERMINALCO.,LTD (WATER)</t>
+          <t>HMM LE HAVRE 019W</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2433,22 +2401,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>YM COSMOS</t>
+          <t>HMM LE HAVRE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>YM COSMOS 191E</t>
+          <t>HMM LE HAVRE 019W</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2463,7 +2431,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2473,7 +2441,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2468,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2510,12 +2478,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ONE ORINOCO</t>
+          <t>POSORJA EXPRESS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ONE ORINOCO 2630E</t>
+          <t>POSORJA EXPRESS 2633E</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2525,12 +2493,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>73</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2540,7 +2508,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2567,22 +2535,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HMM OSLO</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>HMM OSLO 020W</t>
+          <t>ONE COMPETENCE 099E</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2592,12 +2560,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2607,7 +2575,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2634,22 +2602,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HMM OSLO</t>
+          <t>HMM VANCOUVER</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>HMM OSLO 020W</t>
+          <t>HMM VANCOUVER 307E</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2659,12 +2627,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2674,7 +2642,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2701,22 +2669,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>YM MOBILITY</t>
+          <t>ONE FOREVER</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>YM MOBILITY 090E</t>
+          <t>ONE FOREVER 010W</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2726,12 +2694,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2741,7 +2709,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2768,22 +2736,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>TENO</t>
+          <t>ONE FOREVER</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>TENO 2631E</t>
+          <t>ONE FOREVER 010W</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2793,12 +2761,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2808,7 +2776,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2835,22 +2803,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ONE FUTURE</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ONE FUTURE 009W</t>
+          <t>HYUNDAI SUPREME 159E</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2860,12 +2828,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2875,7 +2843,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -2902,22 +2870,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ONE FUTURE</t>
+          <t>CONTI CONTESSA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ONE FUTURE 009W</t>
+          <t>CONTI CONTESSA 026E</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2927,12 +2895,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2942,811 +2910,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>PN3</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>HYUNDAI FORWARD</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>HYUNDAI FORWARD 171E</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>AX3</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>SEASPAN ZAMBEZI</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>SEASPAN ZAMBEZI 2632E</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>PN3</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>ONE MODERN</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>ONE MODERN 082E</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>HMM LE HAVRE</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>HMM LE HAVRE 019W</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>HMM LE HAVRE</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>HMM LE HAVRE 019W</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>AX3</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>POSORJA EXPRESS</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>POSORJA EXPRESS 2633E</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>AX4</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>ONE COMPETENCE</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>ONE COMPETENCE 099E</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>PN3</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>HMM VANCOUVER</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>HMM VANCOUVER 307E</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>ONE FOREVER</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>ONE FOREVER 010W</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>FE3</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>ONE FOREVER</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>ONE FOREVER 010W</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>PN3</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>HYUNDAI SUPREME</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>HYUNDAI SUPREME 159E</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>AX4</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>CONTI CONTESSA</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>CONTI CONTESSA 026E</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-11-12</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2026-08-05 07:48 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,7 +518,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -528,12 +528,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 186S</t>
+          <t>ATHENS BRIDGE 1188S</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -595,12 +595,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1188S</t>
+          <t>EMMANUEL P 013S</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>MSC SHUBA B</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>EMMANUEL P 013S</t>
+          <t>MSC SHUBA B FI635A</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MSC SHUBA B</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>MSC SHUBA B FI635A</t>
+          <t>NAVIOS CHRYSALIS 017S</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -786,22 +786,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>MSC AVNI</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 017S</t>
+          <t>MSC AVNI FI636A</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -853,22 +853,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MSC AVNI</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>MSC AVNI FI636A</t>
+          <t>NAVIOS VERDE 187S</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -893,14 +893,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HKHKG→SEGOT</t>
+          <t>HKHKG→NOOSL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SEGOT</t>
+          <t>NOOSL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -930,27 +930,27 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 187S</t>
+          <t>ATHENS BRIDGE 1188S</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GOTHENBURG</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 186S</t>
+          <t>ATHENS BRIDGE 1188S</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 186S</t>
+          <t>EMMANUEL P 013S</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1188S</t>
+          <t>EMMANUEL P 013S</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,22 +1188,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>MSC SHUBA B</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1188S</t>
+          <t>MSC SHUBA B FI635A</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>EMMANUEL P 013S</t>
+          <t>NAVIOS CHRYSALIS 017S</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>EMMANUEL P</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>EMMANUEL P 013S</t>
+          <t>NAVIOS CHRYSALIS 017S</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MSC SHUBA B</t>
+          <t>MSC AVNI</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>MSC SHUBA B FI635A</t>
+          <t>MSC AVNI FI636A</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 017S</t>
+          <t>NAVIOS VERDE 187S</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 017S</t>
+          <t>NAVIOS VERDE 187S</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1563,49 +1563,45 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SX1</t>
-        </is>
-      </c>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MSC AVNI</t>
+          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MSC AVNI FI636A</t>
+          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1615,12 +1611,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,49 +1626,45 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>JSM</t>
-        </is>
-      </c>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 187S</t>
+          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1682,64 +1674,60 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>55</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HONG KONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>JSM</t>
-        </is>
-      </c>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 187S</t>
+          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1749,22 +1737,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>53</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1779,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1812,12 +1800,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1827,7 +1815,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1842,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1875,22 +1863,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1905,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1938,274 +1926,290 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>PN3</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
+          <t>HMM VANCOUVER</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
+          <t>HMM VANCOUVER 307E</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>FE3</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
+          <t>ONE FOREVER</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
+          <t>ONE FOREVER 010W</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>FE3</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
+          <t>ONE FOREVER</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
+          <t>ONE FOREVER 010W</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>CNTAO→ITSPE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>ITSPE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>QINGDAO, SHANDONG</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>AX3</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
+          <t>YOKOHAMA EXPRESS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
+          <t>YOKOHAMA EXPRESS 2634E</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>LA SPEZIA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2236,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2242,12 +2246,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER</t>
+          <t>HYUNDAI SUPREME</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>HMM VANCOUVER 307E</t>
+          <t>HYUNDAI SUPREME 159E</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2257,12 +2261,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2272,7 +2276,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2303,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ONE FOREVER</t>
+          <t>CONTI CONTESSA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ONE FOREVER 010W</t>
+          <t>CONTI CONTESSA 026E</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2324,12 +2328,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2339,7 +2343,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2366,22 +2370,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ONE FOREVER</t>
+          <t>ONE COMPETENCE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ONE FOREVER 010W</t>
+          <t>ONE COMPETENCE 099E</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2391,12 +2395,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2406,7 +2410,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2437,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2443,12 +2447,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>YOKOHAMA EXPRESS</t>
+          <t>POSORJA EXPRESS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>YOKOHAMA EXPRESS 2634E</t>
+          <t>POSORJA EXPRESS 2633E</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2458,12 +2462,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2473,7 +2477,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2500,22 +2504,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME</t>
+          <t>HMM COPENHAGEN</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HYUNDAI SUPREME 159E</t>
+          <t>HMM COPENHAGEN 020W</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2525,12 +2529,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2540,7 +2544,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2567,22 +2571,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA</t>
+          <t>HMM COPENHAGEN</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CONTI CONTESSA 026E</t>
+          <t>HMM COPENHAGEN 020W</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2597,7 +2601,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>61</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2607,7 +2611,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2634,22 +2638,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>POSORJA EXPRESS</t>
+          <t>HYUNDAI COURAGE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>POSORJA EXPRESS 2633E</t>
+          <t>HYUNDAI COURAGE 125E</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2659,7 +2663,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2674,7 +2678,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2701,22 +2705,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>LAW</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE</t>
+          <t>HMM OAKLAND</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ONE COMPETENCE 099E</t>
+          <t>HMM OAKLAND 140E</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2726,7 +2730,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2741,7 +2745,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2768,22 +2772,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HMM COPENHAGEN</t>
+          <t>ACX PEARL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HMM COPENHAGEN 020W</t>
+          <t>ACX PEARL 0291S</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2793,12 +2797,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2808,7 +2812,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2835,22 +2839,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HMM COPENHAGEN</t>
+          <t>MARIA C</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HMM COPENHAGEN 020W</t>
+          <t>MARIA C 197E</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2860,12 +2864,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2875,7 +2879,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2902,22 +2906,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HYUNDAI COURAGE</t>
+          <t>HMM ST PETERSBURG</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>HYUNDAI COURAGE 125E</t>
+          <t>HMM ST PETERSBURG 019W</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2927,12 +2931,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2942,7 +2946,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -2969,22 +2973,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LAW</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HMM OAKLAND</t>
+          <t>HMM ST PETERSBURG</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HMM OAKLAND 140E</t>
+          <t>HMM ST PETERSBURG 019W</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2999,7 +3003,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3009,7 +3013,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -3036,22 +3040,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ACX PEARL</t>
+          <t>ONE DURBAN</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ACX PEARL 0291S</t>
+          <t>ONE DURBAN 001E</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3061,12 +3065,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3076,7 +3080,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -3103,22 +3107,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>MARIA C</t>
+          <t>IQUIQUE EXPRESS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>MARIA C 197E</t>
+          <t>IQUIQUE EXPRESS 2636E</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3128,12 +3132,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3143,7 +3147,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -3170,22 +3174,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HMM ST PETERSBURG</t>
+          <t>YM WEALTH</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>HMM ST PETERSBURG 019W</t>
+          <t>YM WEALTH 193E</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3195,12 +3199,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3210,7 +3214,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -3237,22 +3241,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HMM ST PETERSBURG</t>
+          <t>MARIA C</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>HMM ST PETERSBURG 019W</t>
+          <t>MARIA C 198E</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3262,12 +3266,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3277,7 +3281,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -3304,22 +3308,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ONE DURBAN</t>
+          <t>BRIGHT SAKURA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>ONE DURBAN 001E</t>
+          <t>BRIGHT SAKURA 0021S</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3334,7 +3338,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3344,7 +3348,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -3371,22 +3375,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>IQUIQUE EXPRESS</t>
+          <t>ONE DIAMOND</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>IQUIQUE EXPRESS 2636E</t>
+          <t>ONE DIAMOND 004E</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3401,7 +3405,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3411,7 +3415,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -3438,22 +3442,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>YM WEALTH</t>
+          <t>HMM ROTTERDAM</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>YM WEALTH 193E</t>
+          <t>HMM ROTTERDAM 020W</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3463,12 +3467,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>51</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3478,7 +3482,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -3505,22 +3509,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MARIA C</t>
+          <t>HMM ROTTERDAM</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>MARIA C 198E</t>
+          <t>HMM ROTTERDAM 020W</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3530,12 +3534,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3545,7 +3549,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -3572,22 +3576,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>BRIGHT SAKURA</t>
+          <t>SAPPHIRE TOWER</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>BRIGHT SAKURA 0021S</t>
+          <t>SAPPHIRE TOWER 005E</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3602,7 +3606,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3612,7 +3616,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -3639,22 +3643,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ONE DIAMOND</t>
+          <t>YM COSMOS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ONE DIAMOND 004E</t>
+          <t>YM COSMOS 192E</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3664,12 +3668,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>84</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3679,7 +3683,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -3706,22 +3710,22 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>HMM ROTTERDAM</t>
+          <t>ONE SPARKLE</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>HMM ROTTERDAM 020W</t>
+          <t>ONE SPARKLE 2637E</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3731,12 +3735,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3746,7 +3750,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>
@@ -3773,22 +3777,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>HMM ROTTERDAM</t>
+          <t>ONE DIAMOND</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>HMM ROTTERDAM 020W</t>
+          <t>ONE DIAMOND 005E</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3798,12 +3802,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3813,141 +3817,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-08-27 07:46 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>AX4</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>SAPPHIRE TOWER</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>SAPPHIRE TOWER 005E</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>2026-12-03</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>2026-08-27 07:46 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>PN3</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>YM COSMOS</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>YM COSMOS 192E</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>2026-12-17</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>2026-08-27 07:46 UTC</t>
+          <t>2026-08-28 09:51 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-04 03:10 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-04 03:10 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-04 03:10 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-04 03:10 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-04 03:10 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-04 03:10 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-09-04 03:10 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-04 03:10 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-04 03:10 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-04 03:10 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-04 03:10 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-04 03:10 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-09-04 03:10 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-09-04 03:10 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-09-04 03:10 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-09-04 03:10 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2031,22 +2031,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HMM COPENHAGEN</t>
+          <t>POSORJA EXPRESS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>HMM COPENHAGEN 020W</t>
+          <t>POSORJA EXPRESS 2633E</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2056,12 +2056,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2098,22 +2098,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>LAW</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HMM COPENHAGEN</t>
+          <t>HMM OAKLAND</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>HMM COPENHAGEN 020W</t>
+          <t>HMM OAKLAND 140E</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2123,12 +2123,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2165,22 +2165,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>POSORJA EXPRESS</t>
+          <t>ACX PEARL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>POSORJA EXPRESS 2633E</t>
+          <t>ACX PEARL 0291S</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2232,22 +2232,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>LAW</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HMM OAKLAND</t>
+          <t>HYUNDAI COURAGE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>HMM OAKLAND 140E</t>
+          <t>HYUNDAI COURAGE 125E</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2299,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ACX PEARL</t>
+          <t>HMM ST PETERSBURG</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ACX PEARL 0291S</t>
+          <t>HMM ST PETERSBURG 019W</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2371,17 +2371,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HYUNDAI COURAGE</t>
+          <t>HMM ST PETERSBURG</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>HYUNDAI COURAGE 125E</t>
+          <t>HMM ST PETERSBURG 019W</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2438,17 +2438,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HMM ST PETERSBURG</t>
+          <t>MARIA C</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>HMM ST PETERSBURG 019W</t>
+          <t>MARIA C 197E</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2500,22 +2500,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HMM ST PETERSBURG</t>
+          <t>IQUIQUE EXPRESS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>HMM ST PETERSBURG 019W</t>
+          <t>IQUIQUE EXPRESS 2636E</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2567,22 +2567,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MARIA C</t>
+          <t>YM WEALTH</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MARIA C 197E</t>
+          <t>YM WEALTH 193E</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2634,22 +2634,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>IQUIQUE EXPRESS</t>
+          <t>BRIGHT SAKURA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>IQUIQUE EXPRESS 2636E</t>
+          <t>BRIGHT SAKURA 0021S</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2701,22 +2701,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>YM WEALTH</t>
+          <t>MARIA C</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>YM WEALTH 193E</t>
+          <t>MARIA C 198E</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2768,22 +2768,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>BRIGHT SAKURA</t>
+          <t>SAPPHIRE TOWER</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>BRIGHT SAKURA 0021S</t>
+          <t>SAPPHIRE TOWER 005E</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2840,17 +2840,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MARIA C</t>
+          <t>HMM ROTTERDAM</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>MARIA C 198E</t>
+          <t>HMM ROTTERDAM 020W</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2907,17 +2907,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SAPPHIRE TOWER</t>
+          <t>HMM ROTTERDAM</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SAPPHIRE TOWER 005E</t>
+          <t>HMM ROTTERDAM 020W</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -2969,22 +2969,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HMM ROTTERDAM</t>
+          <t>ONE DURBAN</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>HMM ROTTERDAM 020W</t>
+          <t>ONE DURBAN 001E</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -3036,22 +3036,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HMM ROTTERDAM</t>
+          <t>ONE DIAMOND</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>HMM ROTTERDAM 020W</t>
+          <t>ONE DIAMOND 004E</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -3103,22 +3103,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ONE DURBAN</t>
+          <t>ONE SPARKLE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ONE DURBAN 001E</t>
+          <t>ONE SPARKLE 2637E</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -3170,22 +3170,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ONE DIAMOND</t>
+          <t>EMERALD TOWER</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ONE DIAMOND 004E</t>
+          <t>EMERALD TOWER 005E</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -3237,22 +3237,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ONE SPARKLE</t>
+          <t>MARIA C</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ONE SPARKLE 2637E</t>
+          <t>MARIA C 199E</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -3304,22 +3304,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>EMERALD TOWER</t>
+          <t>HMM DRIVE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>EMERALD TOWER 005E</t>
+          <t>HMM DRIVE 061W</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -3376,17 +3376,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>MARIA C</t>
+          <t>HMM DRIVE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>MARIA C 199E</t>
+          <t>HMM DRIVE 061W</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HMM DRIVE</t>
+          <t>ONE SHINE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>HMM DRIVE 061W</t>
+          <t>ONE SHINE 2638E</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -3505,22 +3505,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HMM DRIVE</t>
+          <t>ONE DIAMOND</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>HMM DRIVE 061W</t>
+          <t>ONE DIAMOND 005E</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>
@@ -3572,22 +3572,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ONE SHINE</t>
+          <t>WAN HAI 331</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ONE SHINE 2638E</t>
+          <t>WAN HAI 331 0030S</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3612,74 +3612,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-04 03:11 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>CNTAO→ITSPE</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>ITSPE</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>QINGDAO, SHANDONG</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>IAE</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>ONE DIAMOND</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>ONE DIAMOND 005E</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>LA SPEZIA</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-12-03</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>TRANSSHIPMENT (1)</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2026-09-04 03:11 UTC</t>
+          <t>2026-09-05 03:11 UTC</t>
         </is>
       </c>
     </row>

--- a/output/one_schedules_latest.xlsx
+++ b/output/one_schedules_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,7 +558,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-08 03:17 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -585,22 +585,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>MSC SHUBA B</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 017S</t>
+          <t>MSC SHUBA B FI635A</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>58</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:17 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MSC SHUBA B</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>MSC SHUBA B FI635A</t>
+          <t>NAVIOS CHRYSALIS 017S</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-08 03:17 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-08 03:17 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-08 03:17 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-09-08 03:17 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -960,14 +960,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-09-08 03:17 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HKHKG→NOOSL</t>
+          <t>HKHKG→SEGOT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NOOSL</t>
+          <t>SEGOT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1002,22 +1002,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>EMMANUEL P 013S</t>
+          <t>EMMANUEL P 014S</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ROTTERDAM</t>
+          <t>GOTHENBURG</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 017S</t>
+          <t>EMMANUEL P 013S</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>55</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1188,22 +1188,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS</t>
+          <t>MSC SHUBA B</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NAVIOS CHRYSALIS 017S</t>
+          <t>MSC SHUBA B FI635A</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1255,22 +1255,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MSC SHUBA B</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>MSC SHUBA B FI635A</t>
+          <t>NAVIOS CHRYSALIS 017S</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE</t>
+          <t>NAVIOS CHRYSALIS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NAVIOS VERDE 187S</t>
+          <t>NAVIOS CHRYSALIS 017S</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MSC AVNI</t>
+          <t>NAVIOS VERDE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>MSC AVNI FI636A</t>
+          <t>NAVIOS VERDE 187S</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1523,22 +1523,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JSM</t>
+          <t>SX1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE</t>
+          <t>MSC AVNI</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ATHENS BRIDGE 1189S</t>
+          <t>MSC AVNI FI636A</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1657,22 +1657,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SX1</t>
+          <t>JSM</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PARANA EXPRESS</t>
+          <t>ATHENS BRIDGE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>PARANA EXPRESS 2638W</t>
+          <t>ATHENS BRIDGE 1189S</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1697,45 +1697,49 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>HKHKG→NOOSL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>NOOSL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SX1</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
+          <t>PARANA EXPRESS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
+          <t>PARANA EXPRESS 2638W</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1745,60 +1749,64 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>HKHKG→NOOSL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>NOOSL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>JSM</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
+          <t>EMMANUEL P 014S</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1808,12 +1816,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1823,45 +1831,49 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VNSGN→NOTAE</t>
+          <t>HKHKG→NOOSL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NOTAE</t>
+          <t>NOOSL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CAI MEP</t>
+          <t>HONG KONG</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>JSM</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
+          <t>EMMANUEL P</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
+          <t>EMMANUEL P 014S</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1871,22 +1883,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (3)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1925,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1934,22 +1946,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (2)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1988,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1997,12 +2009,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2012,7 +2024,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2051,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2060,12 +2072,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2075,7 +2087,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2114,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -2123,12 +2135,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2138,208 +2150,196 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CNTAO→ITSPE</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ITSPE</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>QINGDAO, SHANDONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>LAW</t>
-        </is>
-      </c>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HMM OAKLAND</t>
+          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>HMM OAKLAND 140E</t>
+          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>43</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (1)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CNTAO→ITSPE</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ITSPE</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>QINGDAO, SHANDONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>AX4</t>
-        </is>
-      </c>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HYUNDAI COURAGE</t>
+          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>HYUNDAI COURAGE 125E</t>
+          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (1)</t>
+          <t>TRANSSHIPMENT (3)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CNTAO→ITSPE</t>
+          <t>VNSGN→NOTAE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CNTAO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ITSPE</t>
+          <t>NOTAE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>QINGDAO, SHANDONG</t>
+          <t>CAI MEP</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>CTP</t>
-        </is>
-      </c>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ACX PEARL</t>
+          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ACX PEARL 0291S</t>
+          <t>CONG TY TNHH CANG QUOC TE TAN CANG CAI MEP (WATER)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LA SPEZIA</t>
+          <t>ROTTERDAM</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TRANSSHIPMENT (1)</t>
+          <t>TRANSSHIPMENT (2)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:20 UTC</t>
         </is>
       </c>
     </row>
@@ -2366,22 +2366,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>LAW</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HMM ST PETERSBURG</t>
+          <t>HMM OAKLAND</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>HMM ST PETERSBURG 019W</t>
+          <t>HMM OAKLAND 140E</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -2438,17 +2438,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HMM ST PETERSBURG</t>
+          <t>HYUNDAI COURAGE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>HMM ST PETERSBURG 019W</t>
+          <t>HYUNDAI COURAGE 125E</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -2500,22 +2500,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MARIA C</t>
+          <t>ACX PEARL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MARIA C 197E</t>
+          <t>ACX PEARL 0291S</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -2567,22 +2567,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>IQUIQUE EXPRESS</t>
+          <t>HMM ST PETERSBURG</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>IQUIQUE EXPRESS 2636E</t>
+          <t>HMM ST PETERSBURG 019W</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -2634,22 +2634,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>YM WEALTH</t>
+          <t>HMM ST PETERSBURG</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>YM WEALTH 193E</t>
+          <t>HMM ST PETERSBURG 019W</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -2701,22 +2701,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>BRIGHT SAKURA</t>
+          <t>MARIA C</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>BRIGHT SAKURA 0021S</t>
+          <t>MARIA C 197E</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -2768,22 +2768,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HMM ROTTERDAM</t>
+          <t>YM WEALTH</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>HMM ROTTERDAM 020W</t>
+          <t>YM WEALTH 193E</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -2835,22 +2835,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HMM ROTTERDAM</t>
+          <t>IQUIQUE EXPRESS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>HMM ROTTERDAM 020W</t>
+          <t>IQUIQUE EXPRESS 2636E</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -2902,22 +2902,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>CTP</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MARIA C</t>
+          <t>BRIGHT SAKURA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>MARIA C 198E</t>
+          <t>BRIGHT SAKURA 0021S</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -2969,22 +2969,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AX4</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SAPPHIRE TOWER</t>
+          <t>HMM ROTTERDAM</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SAPPHIRE TOWER 005E</t>
+          <t>HMM ROTTERDAM 020W</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -3036,22 +3036,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PN3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ONE DURBAN</t>
+          <t>HMM ROTTERDAM</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ONE DURBAN 001E</t>
+          <t>HMM ROTTERDAM 020W</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ONE DIAMOND</t>
+          <t>MARIA C</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ONE DIAMOND 004E</t>
+          <t>MARIA C 198E</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>73</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -3170,22 +3170,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>PN3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ONE SPARKLE</t>
+          <t>ONE DURBAN</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ONE SPARKLE 2637E</t>
+          <t>ONE DURBAN 001E</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -3237,22 +3237,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>IAE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HMM DRIVE</t>
+          <t>ONE DIAMOND</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>HMM DRIVE 061W</t>
+          <t>ONE DIAMOND 004E</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -3304,22 +3304,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FE3</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HMM DRIVE</t>
+          <t>ONE SPARKLE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>HMM DRIVE 061W</t>
+          <t>ONE SPARKLE 2637E</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>EMERALD TOWER</t>
+          <t>SAPPHIRE TOWER</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>EMERALD TOWER 005E</t>
+          <t>SAPPHIRE TOWER 005E</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>MARIA C</t>
+          <t>HMM DRIVE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>MARIA C 199E</t>
+          <t>HMM DRIVE 061W</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>49</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -3510,17 +3510,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AX3</t>
+          <t>FE3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ONE SHINE</t>
+          <t>HMM DRIVE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>ONE SHINE 2638E</t>
+          <t>HMM DRIVE 061W</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -3572,22 +3572,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>IAE</t>
+          <t>AX4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ONE DIAMOND</t>
+          <t>EMERALD TOWER</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ONE DIAMOND 005E</t>
+          <t>EMERALD TOWER 005E</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -3639,22 +3639,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CTP</t>
+          <t>AX3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>WAN HAI 331</t>
+          <t>ONE SHINE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>WAN HAI 331 0030S</t>
+          <t>ONE SHINE 2638E</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-08 03:18 UTC</t>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
@@ -3706,47 +3706,248 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>IAE</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>MARIA C</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>MARIA C 199E</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-09-09 03:21 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>IAE</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ONE DIAMOND</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ONE DIAMOND 005E</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-09-09 03:21 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>CTP</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>WAN HAI 331</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>WAN HAI 331 0030S</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>LA SPEZIA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-12-17</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>TRANSSHIPMENT (1)</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09-09 03:21 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CNTAO→ITSPE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CNTAO</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ITSPE</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>QINGDAO, SHANDONG</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>AX4</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>HYUNDAI BRAVE</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>HYUNDAI BRAVE 120E</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>LA SPEZIA</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>2026-12-17</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>TRANSSHIPMENT (1)</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2026-09-08 03:18 UTC</t>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09-09 03:21 UTC</t>
         </is>
       </c>
     </row>
